--- a/docs/candidatos_bebe_v12.xlsx
+++ b/docs/candidatos_bebe_v12.xlsx
@@ -505,7 +505,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,7 +542,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -571,7 +579,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -604,7 +616,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,7 +653,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -670,7 +690,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +727,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -736,7 +764,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -769,7 +801,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -802,7 +838,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -835,7 +875,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -868,7 +912,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -901,7 +949,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -934,7 +986,11 @@
           <t>vestuario/buzo</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -967,7 +1023,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1000,7 +1060,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1033,7 +1097,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1066,7 +1134,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1099,7 +1171,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1132,7 +1208,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1198,7 +1278,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1231,7 +1315,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1264,7 +1352,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1297,7 +1389,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1330,7 +1426,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1363,7 +1463,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1396,7 +1500,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1429,7 +1537,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1462,7 +1574,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1495,7 +1611,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1528,7 +1648,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1561,7 +1685,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1594,7 +1722,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1627,7 +1759,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1660,7 +1796,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1693,7 +1833,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1726,7 +1870,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1759,7 +1907,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1792,7 +1944,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1825,7 +1981,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1858,7 +2018,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1891,7 +2055,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1924,7 +2092,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1957,7 +2129,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1990,7 +2166,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2023,7 +2203,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2056,7 +2240,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2089,7 +2277,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2122,7 +2314,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2155,7 +2351,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2188,7 +2388,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2254,7 +2458,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2287,7 +2495,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2320,7 +2532,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2353,7 +2569,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2386,7 +2606,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2419,7 +2643,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2452,7 +2680,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2485,7 +2717,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2518,7 +2754,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2551,7 +2791,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2584,7 +2828,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2617,7 +2865,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2650,7 +2902,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2683,7 +2939,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2716,7 +2976,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2749,7 +3013,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2782,7 +3050,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2815,7 +3087,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2848,7 +3124,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2881,7 +3161,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2914,7 +3198,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2947,7 +3235,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2980,7 +3272,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3013,7 +3309,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3046,7 +3346,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3079,7 +3383,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3112,7 +3420,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3145,7 +3457,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3178,7 +3494,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3211,7 +3531,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3244,7 +3568,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3277,7 +3605,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3310,7 +3642,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3343,7 +3679,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3376,7 +3716,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3409,7 +3753,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3442,7 +3790,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3475,7 +3827,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3508,7 +3864,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3541,7 +3901,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3574,7 +3938,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3607,7 +3975,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3640,7 +4012,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3673,7 +4049,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3706,7 +4086,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3739,7 +4123,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3772,7 +4160,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3805,7 +4197,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3838,7 +4234,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3871,7 +4271,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3904,7 +4308,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3937,7 +4345,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3970,7 +4382,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4003,7 +4419,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4036,7 +4456,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4069,7 +4493,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4102,7 +4530,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4135,7 +4567,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4168,7 +4604,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4201,7 +4641,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4234,7 +4678,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4267,7 +4715,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4300,7 +4752,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4333,7 +4789,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4366,7 +4826,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4399,7 +4863,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4432,7 +4900,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4465,7 +4937,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4498,7 +4974,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4531,7 +5011,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4564,7 +5048,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4597,7 +5085,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4630,7 +5122,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4663,7 +5159,11 @@
           <t>accesorios/accvest</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4696,7 +5196,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4729,7 +5233,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4762,7 +5270,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4795,7 +5307,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4828,7 +5344,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4861,7 +5381,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4894,7 +5418,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4927,7 +5455,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4960,7 +5492,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4993,7 +5529,11 @@
           <t>calzado/ballerinas</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5026,7 +5566,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5059,7 +5603,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5092,7 +5640,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5125,7 +5677,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5158,7 +5714,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5191,7 +5751,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5224,7 +5788,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5257,7 +5825,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5290,7 +5862,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5323,7 +5899,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5356,7 +5936,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5389,7 +5973,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5422,7 +6010,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5455,7 +6047,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5488,7 +6084,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5521,7 +6121,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5554,7 +6158,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5587,7 +6195,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5620,7 +6232,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5653,7 +6269,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5686,7 +6306,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5719,7 +6343,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5752,7 +6380,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5785,7 +6417,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5818,7 +6454,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5851,7 +6491,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5884,7 +6528,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5917,7 +6565,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5950,7 +6602,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5983,7 +6639,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6016,7 +6676,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6049,7 +6713,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6082,7 +6750,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6115,7 +6787,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6148,7 +6824,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6181,7 +6861,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6214,7 +6898,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6247,7 +6935,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6280,7 +6972,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6313,7 +7009,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6346,7 +7046,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6379,7 +7083,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6412,7 +7120,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6445,7 +7157,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6478,7 +7194,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6511,7 +7231,11 @@
           <t>calzado/gateadores</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6544,7 +7268,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6577,7 +7305,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6610,7 +7342,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6643,7 +7379,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6676,7 +7416,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6709,7 +7453,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6742,7 +7490,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6775,7 +7527,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6808,7 +7564,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6841,7 +7601,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6874,7 +7638,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6907,7 +7675,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6940,7 +7712,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6973,7 +7749,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7006,7 +7786,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7039,7 +7823,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7072,7 +7860,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7105,7 +7897,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7138,7 +7934,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7171,7 +7971,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7204,7 +8008,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7237,7 +8045,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7270,7 +8082,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7303,7 +8119,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7336,7 +8156,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7369,7 +8193,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7402,7 +8230,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7435,7 +8267,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7468,7 +8304,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7501,7 +8341,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7534,7 +8378,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7567,7 +8415,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7600,7 +8452,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7633,7 +8489,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7666,7 +8526,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7699,7 +8563,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7732,7 +8600,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7765,7 +8637,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7798,7 +8674,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7831,7 +8711,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7864,7 +8748,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7897,7 +8785,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7930,7 +8822,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7963,7 +8859,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7996,7 +8896,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8029,7 +8933,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8062,7 +8970,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8095,7 +9007,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8128,7 +9044,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8161,7 +9081,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8194,7 +9118,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8227,7 +9155,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8260,7 +9192,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8293,7 +9229,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8326,7 +9266,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8359,7 +9303,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8392,7 +9340,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8425,7 +9377,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8458,7 +9414,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8491,7 +9451,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8524,7 +9488,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8557,7 +9525,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8590,7 +9562,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8623,7 +9599,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8656,7 +9636,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8689,7 +9673,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8722,7 +9710,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8755,7 +9747,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8788,7 +9784,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8821,7 +9821,11 @@
           <t>calzado/botines</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8854,7 +9858,11 @@
           <t>calzado/mocasin</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8887,7 +9895,11 @@
           <t>calzado/botas</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8920,7 +9932,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8953,7 +9969,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8986,7 +10006,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -9019,7 +10043,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -9052,7 +10080,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -9085,7 +10117,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -9118,7 +10154,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -9151,7 +10191,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -9184,7 +10228,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -9217,7 +10265,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -9250,7 +10302,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -9283,7 +10339,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9316,7 +10376,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9349,7 +10413,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9382,7 +10450,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9415,7 +10487,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9448,7 +10524,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9481,7 +10561,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9514,7 +10598,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9547,7 +10635,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9580,7 +10672,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9613,7 +10709,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9646,7 +10746,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9679,7 +10783,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9712,7 +10820,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9745,7 +10857,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9778,7 +10894,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9811,7 +10931,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9844,7 +10968,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9877,7 +11005,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9910,7 +11042,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9943,7 +11079,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9976,7 +11116,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -10009,7 +11153,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -10042,7 +11190,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -10075,7 +11227,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -10108,7 +11264,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -10141,7 +11301,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -10174,7 +11338,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -10207,7 +11375,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -10240,7 +11412,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -10273,7 +11449,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -10306,7 +11486,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -10339,7 +11523,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -10372,7 +11560,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -10405,7 +11597,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -10438,7 +11634,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -10471,7 +11671,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -10504,7 +11708,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -10537,7 +11745,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -10570,7 +11782,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -10603,7 +11819,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -10636,7 +11856,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -10669,7 +11893,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -10702,7 +11930,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -10735,7 +11967,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -10768,7 +12004,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -10801,7 +12041,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -10834,7 +12078,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -10867,7 +12115,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -10900,7 +12152,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10933,7 +12189,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10966,7 +12226,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10999,7 +12263,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -11032,7 +12300,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -11065,7 +12337,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -11098,7 +12374,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -11131,7 +12411,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -11164,7 +12448,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -11197,7 +12485,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -11230,7 +12522,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -11263,7 +12559,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -11296,7 +12596,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -11329,7 +12633,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -11362,7 +12670,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -11395,7 +12707,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -11428,7 +12744,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -11461,7 +12781,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -11494,7 +12818,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -11527,7 +12855,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -11560,7 +12892,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -11593,7 +12929,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -11626,7 +12966,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -11659,7 +13003,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -11692,7 +13040,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -11725,7 +13077,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -11758,7 +13114,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -11791,7 +13151,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -11824,7 +13188,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -11857,7 +13225,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -11890,7 +13262,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -11923,7 +13299,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -11956,7 +13336,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -11989,7 +13373,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -12022,7 +13410,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -12055,7 +13447,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -12088,7 +13484,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -12121,7 +13521,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -12154,7 +13558,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -12187,7 +13595,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -12220,7 +13632,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -12253,7 +13669,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -12286,7 +13706,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -12319,7 +13743,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -12352,7 +13780,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -12385,7 +13817,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -12418,7 +13854,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -12451,7 +13891,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -12484,7 +13928,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -12517,7 +13965,11 @@
           <t>calzado/sandalias</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -12550,7 +14002,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -12583,7 +14039,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -12616,7 +14076,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -12649,7 +14113,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -12682,7 +14150,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -12715,7 +14187,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -12748,7 +14224,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -12781,7 +14261,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -12814,7 +14298,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -12847,7 +14335,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -12880,7 +14372,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -12913,7 +14409,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -12946,7 +14446,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -12979,7 +14483,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -13012,7 +14520,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -13045,7 +14557,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -13078,7 +14594,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -13111,7 +14631,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -13144,7 +14668,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -13177,7 +14705,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -13210,7 +14742,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -13243,7 +14779,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -13276,7 +14816,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -13309,7 +14853,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -13342,7 +14890,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -13375,7 +14927,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -13408,7 +14964,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -13441,7 +15001,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -13474,7 +15038,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -13507,7 +15075,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -13540,7 +15112,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -13606,7 +15182,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -13639,7 +15219,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -13672,7 +15256,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -13705,7 +15293,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -13738,7 +15330,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -13771,7 +15367,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -13804,7 +15404,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -13837,7 +15441,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -13870,7 +15478,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -13903,7 +15515,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -13936,7 +15552,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -13969,7 +15589,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -14002,7 +15626,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -14035,7 +15663,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -14068,7 +15700,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -14101,7 +15737,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -14134,7 +15774,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -14167,7 +15811,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -14200,7 +15848,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -14233,7 +15885,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -14266,7 +15922,11 @@
           <t>accesorios/guantes</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -14299,7 +15959,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -14332,7 +15996,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -14365,7 +16033,11 @@
           <t>accesorios/accdep</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -14398,7 +16070,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -14431,7 +16107,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -14464,7 +16144,11 @@
           <t>calzado/zapatillas</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -14497,7 +16181,11 @@
           <t>accesorios/medias</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -14530,7 +16218,11 @@
           <t>vestuario/buzo</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -14563,7 +16255,11 @@
           <t>vestuario/buzo</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G428"/>
